--- a/output/graficos_regionales_sexo_edad/plot_intra_p_monto_aps_a_2020_antofagasta.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_p_monto_aps_a_2020_antofagasta.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:25</t>
+    <t xml:space="preserve">2026-09-09 21:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_intra_p_monto_aps_a_2020_antofagasta.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_p_monto_aps_a_2020_antofagasta.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 21:29</t>
+    <t xml:space="preserve">2026-09-18 09:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -73,16 +73,16 @@
     <t xml:space="preserve">Tramo de edad</t>
   </si>
   <si>
-    <t xml:space="preserve">65 a 69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70 a 74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75 a 79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80 y mas</t>
+    <t xml:space="preserve">65 a 69 años</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70 a 74 años</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75 a 79 años</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desde 80 años</t>
   </si>
 </sst>
 </file>

--- a/output/graficos_regionales_sexo_edad/plot_intra_p_monto_aps_a_2020_antofagasta.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_p_monto_aps_a_2020_antofagasta.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 09:27</t>
+    <t xml:space="preserve">2026-09-25 21:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_intra_p_monto_aps_a_2020_antofagasta.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_p_monto_aps_a_2020_antofagasta.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-25 21:46</t>
+    <t xml:space="preserve">2026-10-05 02:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
